--- a/Result/checksun_type/乳製品.xlsx
+++ b/Result/checksun_type/乳製品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>24.59</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>362313.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1052373.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1052373.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1724872.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>3768786.32</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>3768786.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-454470.2067396857</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>362313</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>362313.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>24.5</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>25.39</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2685569.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1143801.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1143801.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1993560.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3828355.94</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>3828355.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-403984.9148765339</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2685569</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2685569.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>24.33</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>25.04</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>25.04</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>458252.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>743127.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>743127</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2134855.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3800461.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3800461.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-566355.3223978691</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>458252</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>458252.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>24.33</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25.01</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>379957.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>984452.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>984452.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2283448.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3807677.76</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>3807677.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-539444.9644855671</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>379957</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>379957.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>24.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>24.97</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>24.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1375776.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1479745.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1479745.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2418095.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3838367.98</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>3838367.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-473346.9544506513</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1375776</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1375776.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>24.61</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>24.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>819454.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2397372.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2397372.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2566061.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3835251.52</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>3835251.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-468710.8703132481</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>819454</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>819454.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>24.88</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>25.79</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>24.89</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>682196.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2843319.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2843319.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2645999.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>3848723.86</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>3848723.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-385742.2904629135</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>682196</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>682196.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>25.29</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>24.85</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1664880.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3526583.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3526583.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2769003.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>3846478.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>3846478.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-238733.0231601885</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1664880</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1664880.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>25.55</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>2856422.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3582444.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3582444.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2855965.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>3821745.94</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>3821745.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-125481.1761862887</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>2856422</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2856422.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>25.72</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5963909.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3356445.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>3356445.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2886618.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>3796028.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>3796028.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-86876.56707406417</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5963909</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5963909.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>25.87</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>24.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3049189.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2734750.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2734750.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2389197.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>3719031.7</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>3719031.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-361569.4266610988</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3049189</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3049189.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>74.96000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>77.55</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>77.55</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>580572021.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>761372434.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>761372434.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>713281953.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>591852182.46</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>591852182.46</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>20200160.18291521</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>580572021</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>580572021.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>74.88</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>76.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>77.62</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>77.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>567170176.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>759956482.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>759956482.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>715597438.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>592899846.08</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>592899846.08</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>37783327.83082056</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>567170176</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>567170176.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>74.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>77.71</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>77.70999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1247043677.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>796813281.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>796813281.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>764355055.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>596823360.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>596823360.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>62988646.15529895</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1247043677</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1247043677.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>74.93999999999998</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>76.69</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>77.8</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>930432408.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>670962016.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>670962016.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>719097614.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>590012176.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>590012176.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>23903059.86329317</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>930432408</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>930432408.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>75.02000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>76.95</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>77.89</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>77.89</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>481643890.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>588803301.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>588803301.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>707272105.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>582215741.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>582215741.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1135463.27245307</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>481643890</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>481643890.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>74.98</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>77.95</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>77.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>573492261.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>665191472.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>665191472</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>712646224.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>580329214.24</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>580329214.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>16654257.09723663</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>573492261</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>573492261.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>75.08</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>77.36</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>78.01</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>78.01000000000001</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>751454172.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>671238394.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>671238394.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>711163123.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>577360400.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>577360400.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>28388270.77202618</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>751454172</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>751454172.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>75.08</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>77.54</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>78.07</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>77.54000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>78.06999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>617787350.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>731896830.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>731896830.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>680237061.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>569229272.66</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>569229272.66</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>25069933.02986753</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>617787350</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>617787350.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>75.16</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>77.69</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>78.13</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>78.13</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>519638836.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>767233213.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>767233213.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>657550176.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>565262583.96</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>565262583.96</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>33755541.00428843</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>519638836</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>519638836.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>75.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>77.82</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>78.18</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>78.18000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>863584741.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>825740908.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>825740908.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>656886555.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>560988698.04</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>560988698.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>55473909.57473648</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>863584741</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>863584741.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>75.94000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>77.95</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>78.23</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>78.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>603726875.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>760100977.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>760100977.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>620276259.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>561962584.56</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>561962584.5599999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>47667592.36913598</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>603726875</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>603726875.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>15.18</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>4596917.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>3279241.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>3279241</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4133860.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3677240.78</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3677240.78</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>98605.48098267242</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>4596917</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>4596917.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>14.86</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>15.19</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>15.19</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>3930958.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>3128966.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>3128966.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4002896.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>3699799.16</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>3699799.16</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>28205.11676028185</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>3930958</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>3930958.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>14.87</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15.21</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3631237.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3449483.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3449483</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3824303.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3704134.96</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3704134.96</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2021.407727429643</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3631237</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3631237.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>2826110.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4301019.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4301019.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3630997.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>3705852.72</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>3705852.72</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-13016.99957675207</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2826110</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2826110.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>14.92</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1410983.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4162838.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4162838.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3564716.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>3682123.92</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>3682123.92</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>58003.51205195673</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1410983</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1410983.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>15.25</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3845543.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4988479.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4988479.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3674459.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>3727140.3</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>3727140.3</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>309010.5818053996</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3845543</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3845543.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>15.27</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>5533542.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4876827.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4876827.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3752350.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3700419.8</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3700419.8</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>395710.3035315536</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>5533542</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>5533542.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15.28</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>7888920.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4199123.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4199123.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3484214.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>3634499.9</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>3634499.9</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>324577.5022999323</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>7888920</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>7888920.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>15.07</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2135204.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>2960976.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>2960976.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2909465.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>3530066.62</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>3530066.62</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-40994.76739880955</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2135204</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2135204.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>5539188.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2966594.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2966594</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3042316.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>3551181.96</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>3551181.96</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>54692.80329580279</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5539188</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5539188.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>15.1</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3287284.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2360440.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2360440.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2852335.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>3481032.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>3481032.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-175276.5529724583</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3287284</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3287284.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/乳製品.xlsx
+++ b/Result/checksun_type/乳製品.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.071</t>
+          <t>99.955</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,159 +963,159 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-5.74</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-7.11</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -1123,88 +1123,88 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25.68</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25.45</v>
+        <v>25.48</v>
       </c>
       <c r="BA2" t="n">
-        <v>25.37</v>
+        <v>25.36</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="BD2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0.18</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0.19</v>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-80.65</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>1823551.2</v>
+        <v>2000443.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1963035.9</t>
+          <t>2122149.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>2019978.34</v>
+        <v>2031795.44</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-139484</t>
+          <t>-121706</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>35797.4778254221</t>
+          <t>37476.70396497366</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3633.723139818991</t>
+          <t>46712.44773250725</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.513</t>
+          <t>69.071</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,63 +1631,63 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.68</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25.42</v>
+        <v>25.45</v>
       </c>
       <c r="BA3" t="n">
         <v>25.37</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE3" t="n">
         <v>0.19</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>2103734.6</v>
+        <v>1823551.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2086915.5</t>
+          <t>1963035.9</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>2151350.3</v>
+        <v>2019978.34</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>-139484</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>41645.43322280449</t>
+          <t>35797.4778254221</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>25762.98360955669</t>
+          <t>3633.723139818991</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.888</t>
+          <t>49.513</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,159 +1937,159 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>26.20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>54.67</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.74</v>
+        <v>-0.66</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25.38</v>
+        <v>25.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-80.56</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>2579144.2</v>
+        <v>2103734.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2043674.8</t>
+          <t>2086915.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>2374162.98</v>
+        <v>2151350.3</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>535469</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>44533.15133430409</t>
+          <t>41645.43322280449</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>109014.4991516974</t>
+          <t>25762.98360955669</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>70.995</t>
+          <t>101.888</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>54.67</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25.34</v>
+        <v>25.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>25.37</v>
+        <v>25.38</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-81.75</t>
+          <t>-80.56</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>2526017.6</v>
+        <v>2579144.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1898824.9</t>
+          <t>2043674.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>2413880.3</v>
+        <v>2374162.98</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>627192</t>
+          <t>535469</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>32809.26991295985</t>
+          <t>44533.15133430409</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>77703.61067076656</t>
+          <t>109014.4991516974</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,174 +2896,174 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>70.995</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>63.11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>33.03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.46</v>
+        <v>-1.23</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25.28</v>
+        <v>25.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>25.36</v>
+        <v>25.37</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.70</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-84.21</t>
+          <t>-81.75</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2243855.6</v>
+        <v>2526017.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1834438.9</t>
+          <t>1898824.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2440561.28</v>
+        <v>2413880.3</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>409416</t>
+          <t>627192</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>24646.66250244954</t>
+          <t>32809.26991295985</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>115072.0696026238</t>
+          <t>77703.61067076656</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121.194</t>
+          <t>63.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,47 +3598,47 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25.21</v>
+        <v>25.28</v>
       </c>
       <c r="BA7" t="n">
-        <v>25.32</v>
+        <v>25.36</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>120.12</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-87.75</t>
+          <t>-84.21</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2102520.6</v>
+        <v>2243855.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1922596.3</t>
+          <t>1834438.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2486323.4</v>
+        <v>2440561.28</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>179924</t>
+          <t>409416</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8205.679393326947</t>
+          <t>24646.66250244954</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>184225.794162326</t>
+          <t>115072.0696026238</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,174 +3870,174 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>121.194</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>139.487</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>26.05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,47 +4085,47 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.05</v>
+        <v>0.89</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25.14</v>
+        <v>25.21</v>
       </c>
       <c r="BA8" t="n">
-        <v>25.3</v>
+        <v>25.32</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>165.49</t>
+          <t>120.12</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-91.43</t>
+          <t>-87.75</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2070096.4</v>
+        <v>2102520.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1814538.0</t>
+          <t>1922596.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2484194.04</v>
+        <v>2486323.4</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>255558</t>
+          <t>179924</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-23797.97783740016</t>
+          <t>8205.679393326947</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>115375.5865989607</t>
+          <t>184225.794162326</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>91.088</t>
+          <t>139.487</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.14</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.96</v>
+        <v>1.05</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.93</v>
+        <v>2.57</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25.06</v>
+        <v>25.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>25.28</v>
+        <v>25.3</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>261.02</t>
+          <t>165.49</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-94.98</t>
+          <t>-91.43</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2360146.0</t>
+          <t>3636910.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>1508205.4</v>
+        <v>2070096.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2128345.3</t>
+          <t>1814538.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2500226.38</v>
+        <v>2484194.04</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-620139</t>
+          <t>255558</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-49102.26228037486</t>
+          <t>-23797.97783740016</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-39129.48087009555</t>
+          <t>115375.5865989607</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2360146.0</t>
+          <t>3636910.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.351</t>
+          <t>91.088</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.51</t>
+          <t>-29.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>25.06</v>
       </c>
       <c r="BA10" t="n">
-        <v>25.26</v>
+        <v>25.28</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>586.59</t>
+          <t>261.02</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-98.25</t>
+          <t>-94.98</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>2195596.320334262</t>
+          <t>2197826.105006954</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>422817.0</t>
+          <t>2360146.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>1271632.2</v>
+        <v>1508205.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1941697.4</t>
+          <t>2128345.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2623199.8</v>
+        <v>2500226.38</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-670065</t>
+          <t>-620139</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-50915.495264062</t>
+          <t>-49102.26228037486</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-121657.3815091008</t>
+          <t>-39129.48087009555</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>422817.0</t>
+          <t>2360146.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,208 +5331,208 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13356.417</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10628.462</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-42.24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-10.25</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/10/07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-53.90</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-9.31</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/10/07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>78.1</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2025-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>26.26</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>78.8</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>78.1</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2025-12-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.14</v>
+        <v>0.27</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>76.66</v>
+        <v>76.59</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.36</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-26.14</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-69.00</t>
+          <t>-70.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>721871594.8</v>
+        <v>755123165.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1566009348.4</t>
+          <t>1307241707.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>874147139.14</v>
+        <v>878310192.12</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-844137753</t>
+          <t>-552118542</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>90261713.745554</t>
+          <t>64661902.18753193</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-78589681.75820565</t>
+          <t>-76137061.38158941</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8791.772</t>
+          <t>10628.462</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-53.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,84 +5993,84 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.38</v>
+        <v>-1</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.13</v>
+        <v>1.14</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>76.84</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>76.7</v>
+        <v>76.66</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.36</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="BE12" t="n">
         <v>0.48</v>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-68.96</t>
+          <t>-69.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>988114425.2</v>
+        <v>721871594.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1751817286.0</t>
+          <t>1566009348.4</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>866724470.7</v>
+        <v>874147139.14</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-763702860</t>
+          <t>-844137753</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>120961967.4735103</t>
+          <t>90261713.745554</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-57333758.01915002</t>
+          <t>-78589681.75820565</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8191.283</t>
+          <t>8791.772</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-2.01</v>
+        <v>-1.38</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>78.67999999999999</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>76.73999999999999</v>
+        <v>76.84</v>
       </c>
       <c r="BA13" t="n">
-        <v>76.73</v>
+        <v>76.7</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>77.38</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-70.45</t>
+          <t>-68.96</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1226431475.8</v>
+        <v>988114425.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1923628405.5</t>
+          <t>1751817286.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>861574179.78</v>
+        <v>866724470.7</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-697196929</t>
+          <t>-763702860</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>153379372.1085395</t>
+          <t>120961967.4735103</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-9510563.74838686</t>
+          <t>-57333758.01915002</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7923.656</t>
+          <t>8191.283</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.28</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>69.83</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.17</v>
+        <v>-2.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.67999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>76.66</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>76.77</v>
+        <v>76.73</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>77.38</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>85.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-73.49</t>
+          <t>-70.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1411314970.2</v>
+        <v>1226431475.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1967701017.6</t>
+          <t>1923628405.5</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>854744843.26</v>
+        <v>861574179.78</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-556386047</t>
+          <t>-697196929</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>182995724.0825261</t>
+          <t>153379372.1085395</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>63658512.48657465</t>
+          <t>-9510563.74838686</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10769.048</t>
+          <t>7923.656</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,92 +7294,92 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-28.28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>79.6</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-4.88</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,33 +7475,33 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>84.48</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>69.83</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.12</v>
+        <v>-1.17</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>76.59999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="BA15" t="n">
         <v>76.77</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>154.81</t>
+          <t>85.18</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-79.14</t>
+          <t>-73.49</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1859360249.2</v>
+        <v>1411314970.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1954784789.8</t>
+          <t>1967701017.6</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>853657807.64</v>
+        <v>854744843.26</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-95424540</t>
+          <t>-556386047</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>204693398.9181536</t>
+          <t>182995724.0825261</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>167246393.9477129</t>
+          <t>63658512.48657465</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27059.373</t>
+          <t>10769.048</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.48</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>82.17</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>2.57</v>
+        <v>1.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>76.44</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>76.73</v>
+        <v>76.77</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>257.17</t>
+          <t>154.81</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-87.21</t>
+          <t>-79.14</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>2410147102</v>
+        <v>1859360249.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1891076280.5</t>
+          <t>1954784789.8</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>844173360.7</v>
+        <v>853657807.64</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>519070821</t>
+          <t>-95424540</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>211501945.2764156</t>
+          <t>204693398.9181536</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>283861777.7512066</t>
+          <t>167246393.9477129</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23927.778</t>
+          <t>27059.373</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>72.87</t>
+          <t>82.17</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.28</v>
+        <v>2.57</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>76.25</v>
+        <v>76.44</v>
       </c>
       <c r="BA17" t="n">
-        <v>76.67</v>
+        <v>76.73</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>546.10</t>
+          <t>257.17</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-87.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>2515520146.8</v>
+        <v>2410147102</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1723525396.2</t>
+          <t>1891076280.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>811558988.24</v>
+        <v>844173360.7</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>791994750</t>
+          <t>519070821</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>198345612.0991808</t>
+          <t>211501945.2764156</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>301826726.3365116</t>
+          <t>283861777.7512066</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20071.869</t>
+          <t>23927.778</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>65.61</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,17 +8936,17 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>86.05</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -8955,47 +8955,47 @@
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.74</v>
+        <v>0.28</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>77.88</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>76.09</v>
+        <v>76.25</v>
       </c>
       <c r="BA18" t="n">
         <v>76.67</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>77.33</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1438.70</t>
+          <t>546.10</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-101.67</t>
+          <t>-95.43</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1558262656.0</t>
+          <t>1867529037.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2620825335.2</v>
+        <v>2515520146.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1582549814.3</t>
+          <t>1723525396.2</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>790506148.16</v>
+        <v>811558988.24</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>1038275520</t>
+          <t>791994750</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>179530864.0560298</t>
+          <t>198345612.0991808</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>347081606.5535004</t>
+          <t>301826726.3365116</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1558262656.0</t>
+          <t>1867529037.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36678.256</t>
+          <t>20071.869</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>65.61</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>72.87</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.57</v>
+        <v>-0.74</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>77.36</t>
+          <t>77.88</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>75.97</v>
+        <v>76.09</v>
       </c>
       <c r="BA19" t="n">
         <v>76.67</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>362.46</t>
+          <t>1438.70</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-101.67</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1110824779.125517</t>
+          <t>1111411791.194215</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>2861619531.0</t>
+          <t>1558262656.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2524087065</v>
+        <v>2620825335.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1481535418.6</t>
+          <t>1582549814.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>775509393.5599999</v>
+        <v>790506148.16</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>1042551646</t>
+          <t>1038275520</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>149067092.6928533</t>
+          <t>179530864.0560298</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>432471347.4508595</t>
+          <t>347081606.5535004</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>2861619531.0</t>
+          <t>1558262656.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>432970</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>791.96</t>
+          <t>554.629</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.40</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.22</t>
+          <t>-20.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.96</v>
+        <v>-0.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.11</v>
+        <v>-1.33</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.7</v>
+        <v>14.68</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-27.67</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-124.92</t>
+          <t>-126.77</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>5168210.4</v>
+        <v>5893366.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>3733648.1</t>
+          <t>4258184.0</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>4110798.74</v>
+        <v>4156786.06</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>1434562</t>
+          <t>1635182</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-59889.96809451834</t>
+          <t>19169.23431195425</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>274168.381757481</t>
+          <t>453994.8475475535</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.77</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>212.646</t>
+          <t>791.96</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10416,44 +10416,44 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.62</v>
+        <v>-0.96</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.97</v>
+        <v>-1.11</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>-1.16</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.9</v>
+        <v>14.89</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.09</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-123.47</t>
+          <t>-124.92</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>3236186.8</v>
+        <v>5168210.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2843595.6</t>
+          <t>3733648.1</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>3959256.34</v>
+        <v>4110798.74</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>392591</t>
+          <t>1434562</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-120627.849885791</t>
+          <t>-59889.96809451834</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-363709.3687196756</t>
+          <t>274168.381757481</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>127.048</t>
+          <t>212.646</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,48 +10903,48 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.91</v>
+        <v>-0.97</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.92</v>
+        <v>14.9</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="BD22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BE22" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BE22" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="BF22" t="inlineStr">
         <is>
           <t>0.37</t>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-122.52</t>
+          <t>-123.47</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3316812.4</v>
+        <v>3236186.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2839807.1</t>
+          <t>2843595.6</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>3937193.46</v>
+        <v>3959256.34</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>477005</t>
+          <t>392591</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-76431.21009781194</t>
+          <t>-120627.849885791</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-370632.7490899111</t>
+          <t>-363709.3687196756</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>354.44</t>
+          <t>127.048</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.11</t>
+          <t>-19.39</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,40 +11390,40 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.34</v>
+        <v>-0.48</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="BD23" t="n">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-121.85</t>
+          <t>-122.52</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3365960.4</v>
+        <v>3316812.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>3016978.6</t>
+          <t>2839807.1</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>3926173.22</v>
+        <v>3937193.46</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>477005</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-22940.02119015754</t>
+          <t>-76431.21009781194</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-234607.122865608</t>
+          <t>-370632.7490899111</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,107 +11662,107 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>354.44</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>295.471</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>11.57</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2024-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2024-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-55.79</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2024-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2024-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,44 +11877,44 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.74</v>
+        <v>-0.86</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>14.79</v>
+        <v>14.78</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.94</v>
+        <v>14.93</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BE24" t="n">
         <v>-0.08</v>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-121.40</t>
+          <t>-121.85</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>2623001.2</v>
+        <v>3365960.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5932770.2</t>
+          <t>3016978.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>3872896.32</v>
+        <v>3926173.22</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-3309769</t>
+          <t>348981</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>15544.90638719709</t>
+          <t>-22940.02119015754</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-387022.9381571175</t>
+          <t>-234607.122865608</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12107,17 +12107,17 @@
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
           <t>14.6</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>14.65</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>119.496</t>
+          <t>295.471</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-60.05</t>
+          <t>-55.79</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,40 +12364,40 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.8</v>
+        <v>14.79</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="BD25" t="n">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-121.09</t>
+          <t>-121.40</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>2299085.8</v>
+        <v>2623001.2</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5755023.9</t>
+          <t>5932770.2</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>3887411.24</v>
+        <v>3872896.32</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-3455938</t>
+          <t>-3309769</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>88739.05994070883</t>
+          <t>15544.90638719709</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-500173.1050679483</t>
+          <t>-387022.9381571175</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>238.503</t>
+          <t>119.496</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-59.23</t>
+          <t>-60.05</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,44 +12847,44 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BD26" t="n">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-120.74</t>
+          <t>-121.09</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2451004.4</v>
+        <v>2299085.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>6011676.6</t>
+          <t>5755023.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>3903777.52</v>
+        <v>3887411.24</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-3560672</t>
+          <t>-3455938</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>195813.999033192</t>
+          <t>88739.05994070883</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-368607.9469024232</t>
+          <t>-500173.1050679483</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
           <t>14.7</t>
-        </is>
-      </c>
-      <c r="CR26" t="inlineStr">
-        <is>
-          <t>14.75</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>142.725</t>
+          <t>238.503</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,149 +13138,149 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-59.23</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2024-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-18.84</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/04/02</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-62.51</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2024-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2024-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-18.56</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/04/02</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
       <c r="AI27" t="inlineStr">
         <is>
           <t>2025/11/18</t>
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.14</v>
+        <v>-0.41</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.82</v>
+        <v>14.81</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.97</v>
+        <v>14.96</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BD27" t="n">
         <v>-0.08</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-120.45</t>
+          <t>-120.74</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>2098435.0</t>
+          <t>3494163.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2362801.8</v>
+        <v>2451004.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>6303069.2</t>
+          <t>6011676.6</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>3912242.12</v>
+        <v>3903777.52</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-3940267</t>
+          <t>-3560672</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>298436.1710214856</t>
+          <t>195813.999033192</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-354357.1514194431</t>
+          <t>-368607.9469024232</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>2098435.0</t>
+          <t>3494163.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
           <t>14.75</t>
         </is>
       </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
       <c r="CS27" t="inlineStr">
         <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
           <t>14.65</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>14.7</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,107 +13610,107 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>142.725</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>98.453</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-62.51</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2024-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2024-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-58.81</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2024-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2024-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-18.56</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -13806,17 +13806,17 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
@@ -13825,40 +13825,40 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.83</v>
+        <v>14.82</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.98</v>
+        <v>14.97</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BD28" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-120.35</t>
+          <t>-120.45</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>10873002.70137931</t>
+          <t>10874442.9876033</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1452324.0</t>
+          <t>2098435.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2667996.8</v>
+        <v>2362801.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>6478062.0</t>
+          <t>6303069.2</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3960405.22</v>
+        <v>3912242.12</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-3810065</t>
+          <t>-3940267</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>417125.8660107454</t>
+          <t>298436.1710214856</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-171800.9738930631</t>
+          <t>-354357.1514194431</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1452324.0</t>
+          <t>2098435.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14055,17 +14055,17 @@
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>14.7</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>14.75</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/乳製品.xlsx
+++ b/Result/checksun_type/乳製品.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>99.955</t>
+          <t>33.567</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-16.66</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,92 +1118,92 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AU2" t="n">
         <v>-0.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.27</v>
+        <v>-0.01</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25.48</v>
+        <v>25.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>25.36</v>
+        <v>25.34</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-20.70</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-80.65</t>
+          <t>-81.60</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>2532541.0</t>
+          <t>853500.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>2000443.2</v>
+        <v>1804417.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>2122149.4</t>
+          <t>2165217.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>2031795.44</v>
+        <v>1945762.66</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-121706</t>
+          <t>-360799</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>37476.70396497366</t>
+          <t>23983.62162483565</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>46712.44773250725</t>
+          <t>-50228.33124592341</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2532541.0</t>
+          <t>853500.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>25.45</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>25.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>69.071</t>
+          <t>99.955</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,248 +1450,248 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-5.74</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-7.11</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25.68</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25.45</v>
+        <v>25.48</v>
       </c>
       <c r="BA3" t="n">
-        <v>25.37</v>
+        <v>25.36</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="BD3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE3" t="n">
         <v>0.18</v>
       </c>
-      <c r="BE3" t="n">
-        <v>0.19</v>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-80.65</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>1823551.2</v>
+        <v>2000443.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1963035.9</t>
+          <t>2122149.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>2019978.34</v>
+        <v>2031795.44</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-139484</t>
+          <t>-121706</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>35797.4778254221</t>
+          <t>37476.70396497366</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>3633.723139818991</t>
+          <t>46712.44773250725</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.513</t>
+          <t>69.071</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,63 +2118,63 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.68</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25.42</v>
+        <v>25.45</v>
       </c>
       <c r="BA4" t="n">
         <v>25.37</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE4" t="n">
         <v>0.19</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>2103734.6</v>
+        <v>1823551.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2086915.5</t>
+          <t>1963035.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>2151350.3</v>
+        <v>2019978.34</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>-139484</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>41645.43322280449</t>
+          <t>35797.4778254221</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>25762.98360955669</t>
+          <t>3633.723139818991</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.888</t>
+          <t>49.513</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,177 +2424,177 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>26.20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>54.67</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.74</v>
+        <v>-0.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25.38</v>
+        <v>25.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-80.56</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>2579144.2</v>
+        <v>2103734.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2043674.8</t>
+          <t>2086915.5</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>2374162.98</v>
+        <v>2151350.3</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>535469</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>44533.15133430409</t>
+          <t>41645.43322280449</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>109014.4991516974</t>
+          <t>25762.98360955669</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>70.995</t>
+          <t>101.888</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>54.67</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25.34</v>
+        <v>25.38</v>
       </c>
       <c r="BA6" t="n">
-        <v>25.37</v>
+        <v>25.38</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-81.75</t>
+          <t>-80.56</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2526017.6</v>
+        <v>2579144.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1898824.9</t>
+          <t>2043674.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2413880.3</v>
+        <v>2374162.98</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>627192</t>
+          <t>535469</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>32809.26991295985</t>
+          <t>44533.15133430409</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>77703.61067076656</t>
+          <t>109014.4991516974</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,192 +3383,192 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>70.995</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>63.11</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>33.03</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.46</v>
+        <v>-1.23</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25.28</v>
+        <v>25.34</v>
       </c>
       <c r="BA7" t="n">
-        <v>25.36</v>
+        <v>25.37</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.70</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-84.21</t>
+          <t>-81.75</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2243855.6</v>
+        <v>2526017.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1834438.9</t>
+          <t>1898824.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2440561.28</v>
+        <v>2413880.3</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>409416</t>
+          <t>627192</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>24646.66250244954</t>
+          <t>32809.26991295985</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>115072.0696026238</t>
+          <t>77703.61067076656</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121.194</t>
+          <t>63.11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,47 +4085,47 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25.21</v>
+        <v>25.28</v>
       </c>
       <c r="BA8" t="n">
-        <v>25.32</v>
+        <v>25.36</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>120.12</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-87.75</t>
+          <t>-84.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2102520.6</v>
+        <v>2243855.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1922596.3</t>
+          <t>1834438.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2486323.4</v>
+        <v>2440561.28</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>179924</t>
+          <t>409416</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>8205.679393326947</t>
+          <t>24646.66250244954</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>184225.794162326</t>
+          <t>115072.0696026238</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4357,192 +4357,192 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>121.194</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>139.487</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>26.05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.05</v>
+        <v>0.89</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25.14</v>
+        <v>25.21</v>
       </c>
       <c r="BA9" t="n">
-        <v>25.3</v>
+        <v>25.32</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>165.49</t>
+          <t>120.12</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-91.43</t>
+          <t>-87.75</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2070096.4</v>
+        <v>2102520.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1814538.0</t>
+          <t>1922596.3</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2484194.04</v>
+        <v>2486323.4</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>255558</t>
+          <t>179924</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-23797.97783740016</t>
+          <t>8205.679393326947</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>115375.5865989607</t>
+          <t>184225.794162326</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>91.088</t>
+          <t>139.487</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.14</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,47 +5059,47 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.96</v>
+        <v>1.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.93</v>
+        <v>2.57</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25.06</v>
+        <v>25.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>25.28</v>
+        <v>25.3</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>261.02</t>
+          <t>165.49</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-94.98</t>
+          <t>-91.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>2197826.105006954</t>
+          <t>1398770.206967213</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2360146.0</t>
+          <t>3636910.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>1508205.4</v>
+        <v>2070096.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2128345.3</t>
+          <t>1814538.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2500226.38</v>
+        <v>2484194.04</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-620139</t>
+          <t>255558</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-49102.26228037486</t>
+          <t>-23797.97783740016</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-39129.48087009555</t>
+          <t>115375.5865989607</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2360146.0</t>
+          <t>3636910.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13356.417</t>
+          <t>16831.658</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.25</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>33.10</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.17</v>
+        <v>-1.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.27</v>
+        <v>-0.38</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>76.59</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-26.14</t>
+          <t>-63.14</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-70.90</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1024663694.0</t>
+          <t>1270686079.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>755123165.2</v>
+        <v>884981753.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1307241707.2</t>
+          <t>1148148362.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>878310192.12</v>
+        <v>890513194.8</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-552118542</t>
+          <t>-263166608</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>64661902.18753193</t>
+          <t>46396206.20353962</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-76137061.38158941</t>
+          <t>-54065121.70841813</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1024663694.0</t>
+          <t>1270686079.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10628.462</t>
+          <t>13356.417</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,193 +5833,193 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-42.24</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-10.25</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/10/07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-53.90</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-9.31</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/10/07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>78.1</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2025-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>26.26</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
         <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>78.8</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>78.1</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2025-12-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6033,47 +6033,47 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.14</v>
+        <v>0.27</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>76.66</v>
+        <v>76.59</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.36</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-26.14</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-69.00</t>
+          <t>-70.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>721871594.8</v>
+        <v>755123165.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1566009348.4</t>
+          <t>1307241707.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>874147139.14</v>
+        <v>878310192.12</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-844137753</t>
+          <t>-552118542</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>90261713.745554</t>
+          <t>64661902.18753193</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-78589681.75820565</t>
+          <t>-76137061.38158941</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8791.772</t>
+          <t>10628.462</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-53.90</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,84 +6480,84 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.38</v>
+        <v>-1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.13</v>
+        <v>1.14</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>76.84</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>76.7</v>
+        <v>76.66</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.36</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="BE13" t="n">
         <v>0.48</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-68.96</t>
+          <t>-69.00</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>988114425.2</v>
+        <v>721871594.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1751817286.0</t>
+          <t>1566009348.4</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>866724470.7</v>
+        <v>874147139.14</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-763702860</t>
+          <t>-844137753</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>120961967.4735103</t>
+          <t>90261713.745554</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-57333758.01915002</t>
+          <t>-78589681.75820565</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8191.283</t>
+          <t>8791.772</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-2.01</v>
+        <v>-1.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>78.67999999999999</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>76.73999999999999</v>
+        <v>76.84</v>
       </c>
       <c r="BA14" t="n">
-        <v>76.73</v>
+        <v>76.7</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>77.38</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-70.45</t>
+          <t>-68.96</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1226431475.8</v>
+        <v>988114425.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1923628405.5</t>
+          <t>1751817286.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>861574179.78</v>
+        <v>866724470.7</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-697196929</t>
+          <t>-763702860</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>153379372.1085395</t>
+          <t>120961967.4735103</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-9510563.74838686</t>
+          <t>-57333758.01915002</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7923.656</t>
+          <t>8191.283</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.28</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>69.83</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.17</v>
+        <v>-2.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.67999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>76.66</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>76.77</v>
+        <v>76.73</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>77.38</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>85.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-73.49</t>
+          <t>-70.45</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1411314970.2</v>
+        <v>1226431475.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1967701017.6</t>
+          <t>1923628405.5</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>854744843.26</v>
+        <v>861574179.78</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-556386047</t>
+          <t>-697196929</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>182995724.0825261</t>
+          <t>153379372.1085395</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>63658512.48657465</t>
+          <t>-9510563.74838686</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10769.048</t>
+          <t>7923.656</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,84 +7781,84 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-28.28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>79.6</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-4.88</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>0</t>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,33 +7962,33 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>84.48</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>69.83</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.12</v>
+        <v>-1.17</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>76.59999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="BA16" t="n">
         <v>76.77</v>
@@ -8014,14 +8014,14 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>154.81</t>
+          <t>85.18</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-79.14</t>
+          <t>-73.49</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1859360249.2</v>
+        <v>1411314970.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1954784789.8</t>
+          <t>1967701017.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>853657807.64</v>
+        <v>854744843.26</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-95424540</t>
+          <t>-556386047</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>204693398.9181536</t>
+          <t>182995724.0825261</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>167246393.9477129</t>
+          <t>63658512.48657465</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27059.373</t>
+          <t>10769.048</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.48</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>82.17</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>2.57</v>
+        <v>1.12</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>76.44</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>76.73</v>
+        <v>76.77</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>257.17</t>
+          <t>154.81</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-87.21</t>
+          <t>-79.14</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>2410147102</v>
+        <v>1859360249.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1891076280.5</t>
+          <t>1954784789.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>844173360.7</v>
+        <v>853657807.64</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>519070821</t>
+          <t>-95424540</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>211501945.2764156</t>
+          <t>204693398.9181536</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>283861777.7512066</t>
+          <t>167246393.9477129</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23927.778</t>
+          <t>27059.373</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>72.87</t>
+          <t>82.17</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.28</v>
+        <v>2.57</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>76.25</v>
+        <v>76.44</v>
       </c>
       <c r="BA18" t="n">
-        <v>76.67</v>
+        <v>76.73</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>546.10</t>
+          <t>257.17</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-87.21</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2515520146.8</v>
+        <v>2410147102</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1723525396.2</t>
+          <t>1891076280.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>811558988.24</v>
+        <v>844173360.7</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>791994750</t>
+          <t>519070821</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>198345612.0991808</t>
+          <t>211501945.2764156</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>301826726.3365116</t>
+          <t>283861777.7512066</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20071.869</t>
+          <t>23927.778</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>65.61</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,17 +9423,17 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>86.05</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
@@ -9442,47 +9442,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.74</v>
+        <v>0.28</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>77.88</t>
+          <t>78.17999999999999</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>76.09</v>
+        <v>76.25</v>
       </c>
       <c r="BA19" t="n">
         <v>76.67</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>77.33</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1438.70</t>
+          <t>546.10</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-101.67</t>
+          <t>-95.43</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1111411791.194215</t>
+          <t>1242773822.028689</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1558262656.0</t>
+          <t>1867529037.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2620825335.2</v>
+        <v>2515520146.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1582549814.3</t>
+          <t>1723525396.2</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>790506148.16</v>
+        <v>811558988.24</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>1038275520</t>
+          <t>791994750</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>179530864.0560298</t>
+          <t>198345612.0991808</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>347081606.5535004</t>
+          <t>301826726.3365116</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1558262656.0</t>
+          <t>1867529037.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>432970</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>554.629</t>
+          <t>462.207</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38.40</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.50</t>
+          <t>-20.78</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>17.30</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9929,56 +9929,56 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.33</v>
+        <v>-1.54</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.68</v>
+        <v>14.64</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.87</v>
+        <v>14.85</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-27.67</t>
+          <t>-29.90</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-126.77</t>
+          <t>-276.24</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>7945767.0</t>
+          <t>6601345.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>5893366.8</v>
+        <v>6180211.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>4258184.0</t>
+          <t>4773086.1</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>4156786.06</v>
+        <v>4209988</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>1635182</t>
+          <t>1407125</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>19169.23431195425</t>
+          <t>88172.71401964061</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>453994.8475475535</t>
+          <t>467691.8524119155</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>7945767.0</t>
+          <t>6601345.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-12.77</t>
+          <t>-13.07</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
           <t>14.3</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>14.35</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>791.96</t>
+          <t>554.629</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.40</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.22</t>
+          <t>-20.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10416,56 +10416,56 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.96</v>
+        <v>-0.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.11</v>
+        <v>-1.33</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.7</v>
+        <v>14.68</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-27.67</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-124.92</t>
+          <t>-263.07</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>5168210.4</v>
+        <v>5893366.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3733648.1</t>
+          <t>4258184.0</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>4110798.74</v>
+        <v>4156786.06</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>1434562</t>
+          <t>1635182</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-59889.96809451834</t>
+          <t>19169.23431195425</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>274168.381757481</t>
+          <t>453994.8475475535</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.77</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>212.646</t>
+          <t>791.96</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,56 +10903,56 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.62</v>
+        <v>-0.96</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.97</v>
+        <v>-1.11</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
           <t>-1.16</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.9</v>
+        <v>14.89</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BE22" t="n">
         <v>-0.09</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-123.47</t>
+          <t>-251.79</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3236186.8</v>
+        <v>5168210.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2843595.6</t>
+          <t>3733648.1</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>3959256.34</v>
+        <v>4110798.74</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>392591</t>
+          <t>1434562</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-120627.849885791</t>
+          <t>-59889.96809451834</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-363709.3687196756</t>
+          <t>274168.381757481</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>127.048</t>
+          <t>212.646</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,56 +11390,56 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.91</v>
+        <v>-0.97</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.92</v>
+        <v>14.9</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="BD23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BE23" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BE23" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-122.52</t>
+          <t>-242.95</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3316812.4</v>
+        <v>3236186.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2839807.1</t>
+          <t>2843595.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>3937193.46</v>
+        <v>3959256.34</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>477005</t>
+          <t>392591</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-76431.21009781194</t>
+          <t>-120627.849885791</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-370632.7490899111</t>
+          <t>-363709.3687196756</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>354.44</t>
+          <t>127.048</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-19.11</t>
+          <t>-19.39</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,40 +11877,40 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.34</v>
+        <v>-0.48</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="BD24" t="n">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-121.85</t>
+          <t>-237.19</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3365960.4</v>
+        <v>3316812.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>3016978.6</t>
+          <t>2839807.1</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>3926173.22</v>
+        <v>3937193.46</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>477005</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-22940.02119015754</t>
+          <t>-76431.21009781194</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-234607.122865608</t>
+          <t>-370632.7490899111</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,42 +12149,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>354.44</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>295.471</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-55.79</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -12249,12 +12249,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,56 +12364,56 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.74</v>
+        <v>-0.86</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.79</v>
+        <v>14.78</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.94</v>
+        <v>14.93</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BE25" t="n">
         <v>-0.08</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-121.40</t>
+          <t>-233.09</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>2623001.2</v>
+        <v>3365960.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5932770.2</t>
+          <t>3016978.6</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>3872896.32</v>
+        <v>3926173.22</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-3309769</t>
+          <t>348981</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>15544.90638719709</t>
+          <t>-22940.02119015754</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-387022.9381571175</t>
+          <t>-234607.122865608</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12594,17 +12594,17 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>14.6</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>14.65</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>119.496</t>
+          <t>295.471</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-60.05</t>
+          <t>-55.79</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,12 +12811,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,40 +12851,40 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>14.8</v>
+        <v>14.79</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="BD26" t="n">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-121.09</t>
+          <t>-230.38</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2299085.8</v>
+        <v>2623001.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>5755023.9</t>
+          <t>5932770.2</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>3887411.24</v>
+        <v>3872896.32</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-3455938</t>
+          <t>-3309769</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>88739.05994070883</t>
+          <t>15544.90638719709</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-500173.1050679483</t>
+          <t>-387022.9381571175</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>238.503</t>
+          <t>119.496</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-59.23</t>
+          <t>-60.05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,44 +13334,44 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BD27" t="n">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-120.74</t>
+          <t>-228.47</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2451004.4</v>
+        <v>2299085.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>6011676.6</t>
+          <t>5755023.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>3903777.52</v>
+        <v>3887411.24</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-3560672</t>
+          <t>-3455938</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>195813.999033192</t>
+          <t>88739.05994070883</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-368607.9469024232</t>
+          <t>-500173.1050679483</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
           <t>14.7</t>
-        </is>
-      </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>14.75</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>142.725</t>
+          <t>238.503</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,149 +13625,149 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-2.45</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-59.23</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2024-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2024-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-18.84</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/04/02</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-2.44</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-62.51</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2024-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2024-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-18.56</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/04/02</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
       <c r="AI28" t="inlineStr">
         <is>
           <t>2025/11/18</t>
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,60 +13821,60 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-0.14</v>
+        <v>-0.41</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.82</v>
+        <v>14.81</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.97</v>
+        <v>14.96</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BD28" t="n">
         <v>-0.08</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-120.45</t>
+          <t>-226.36</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>10874442.9876033</t>
+          <t>10299422.54508197</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>2098435.0</t>
+          <t>3494163.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2362801.8</v>
+        <v>2451004.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>6303069.2</t>
+          <t>6011676.6</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3912242.12</v>
+        <v>3903777.52</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-3940267</t>
+          <t>-3560672</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>298436.1710214856</t>
+          <t>195813.999033192</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-354357.1514194431</t>
+          <t>-368607.9469024232</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>2098435.0</t>
+          <t>3494163.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
           <t>14.75</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
       <c r="CS28" t="inlineStr">
         <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>14.65</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>14.7</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/乳製品.xlsx
+++ b/Result/checksun_type/乳製品.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.567</t>
+          <t>51.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,159 +963,159 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-25.17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-16.66</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>2025-12-23 00:00:00</t>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25.5</v>
+        <v>25.51</v>
       </c>
       <c r="BA2" t="n">
-        <v>25.34</v>
+        <v>25.32</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-20.70</t>
+          <t>-33.80</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-81.60</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>853500.0</t>
+          <t>1313209.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>1804417.8</v>
+        <v>1541903.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>2165217.7</t>
+          <t>2060524.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1945762.66</v>
+        <v>1883477.42</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-360799</t>
+          <t>-518620</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>23983.62162483565</t>
+          <t>7624.142413372181</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-50228.33124592341</t>
+          <t>-82352.99324967689</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>853500.0</t>
+          <t>1313209.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>25.3</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>25.45</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>99.955</t>
+          <t>33.567</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-16.66</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,22 +1610,22 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AU3" t="n">
         <v>-0.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.27</v>
+        <v>-0.01</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25.48</v>
+        <v>25.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>25.36</v>
+        <v>25.34</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-20.70</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-80.65</t>
+          <t>-81.60</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>2532541.0</t>
+          <t>853500.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>2000443.2</v>
+        <v>1804417.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2122149.4</t>
+          <t>2165217.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>2031795.44</v>
+        <v>1945762.66</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-121706</t>
+          <t>-360799</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>37476.70396497366</t>
+          <t>23983.62162483565</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>46712.44773250725</t>
+          <t>-50228.33124592341</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2532541.0</t>
+          <t>853500.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
           <t>25.45</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>25.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>69.071</t>
+          <t>99.955</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,159 +1937,159 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-5.74</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-7.11</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>2025-12-23 00:00:00</t>
@@ -2097,22 +2097,22 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
@@ -2123,62 +2123,62 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25.68</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25.45</v>
+        <v>25.48</v>
       </c>
       <c r="BA4" t="n">
-        <v>25.37</v>
+        <v>25.36</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="BD4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE4" t="n">
         <v>0.18</v>
       </c>
-      <c r="BE4" t="n">
-        <v>0.19</v>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-80.65</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>1823551.2</v>
+        <v>2000443.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1963035.9</t>
+          <t>2122149.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>2019978.34</v>
+        <v>2031795.44</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-139484</t>
+          <t>-121706</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>35797.4778254221</t>
+          <t>37476.70396497366</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>3633.723139818991</t>
+          <t>46712.44773250725</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1750407.0</t>
+          <t>2532541.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.513</t>
+          <t>69.071</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,58 +2610,58 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.68</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25.42</v>
+        <v>25.45</v>
       </c>
       <c r="BA5" t="n">
         <v>25.37</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE5" t="n">
         <v>0.19</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>2103734.6</v>
+        <v>1823551.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2086915.5</t>
+          <t>1963035.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>2151350.3</v>
+        <v>2019978.34</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>-139484</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>41645.43322280449</t>
+          <t>35797.4778254221</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>25762.98360955669</t>
+          <t>3633.723139818991</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1259862.0</t>
+          <t>1750407.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101.888</t>
+          <t>49.513</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,159 +2911,159 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>26.20</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>2025-12-23 00:00:00</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>54.67</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.74</v>
+        <v>-0.66</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25.38</v>
+        <v>25.42</v>
       </c>
       <c r="BA6" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-80.56</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2579144.2</v>
+        <v>2103734.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2043674.8</t>
+          <t>2086915.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2374162.98</v>
+        <v>2151350.3</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>535469</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>44533.15133430409</t>
+          <t>41645.43322280449</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>109014.4991516974</t>
+          <t>25762.98360955669</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>2625779.0</t>
+          <t>1259862.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>70.995</t>
+          <t>101.888</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>54.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25.34</v>
+        <v>25.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>25.37</v>
+        <v>25.38</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-81.75</t>
+          <t>-80.56</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2526017.6</v>
+        <v>2579144.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1898824.9</t>
+          <t>2043674.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2413880.3</v>
+        <v>2374162.98</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>627192</t>
+          <t>535469</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>32809.26991295985</t>
+          <t>44533.15133430409</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>77703.61067076656</t>
+          <t>109014.4991516974</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1833627.0</t>
+          <t>2625779.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,174 +3870,174 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>70.995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>63.11</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>33.03</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>2025-12-23 00:00:00</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.46</v>
+        <v>-1.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25.28</v>
+        <v>25.34</v>
       </c>
       <c r="BA8" t="n">
-        <v>25.36</v>
+        <v>25.37</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.70</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-84.21</t>
+          <t>-81.75</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2243855.6</v>
+        <v>2526017.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1834438.9</t>
+          <t>1898824.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2440561.28</v>
+        <v>2413880.3</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>409416</t>
+          <t>627192</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>24646.66250244954</t>
+          <t>32809.26991295985</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>115072.0696026238</t>
+          <t>77703.61067076656</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1648081.0</t>
+          <t>1833627.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>121.194</t>
+          <t>63.11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25.21</v>
+        <v>25.28</v>
       </c>
       <c r="BA9" t="n">
-        <v>25.32</v>
+        <v>25.36</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>120.12</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-87.75</t>
+          <t>-84.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2102520.6</v>
+        <v>2243855.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1922596.3</t>
+          <t>1834438.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2486323.4</v>
+        <v>2440561.28</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>179924</t>
+          <t>409416</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>8205.679393326947</t>
+          <t>24646.66250244954</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>184225.794162326</t>
+          <t>115072.0696026238</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3151324.0</t>
+          <t>1648081.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,174 +4844,174 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>121.194</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.36</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>139.487</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>26.05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>2025-12-23 00:00:00</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,47 +5059,47 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.05</v>
+        <v>0.89</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25.14</v>
+        <v>25.21</v>
       </c>
       <c r="BA10" t="n">
-        <v>25.3</v>
+        <v>25.32</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>165.49</t>
+          <t>120.12</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-91.43</t>
+          <t>-87.75</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1398770.206967213</t>
+          <t>1399937.984662577</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2070096.4</v>
+        <v>2102520.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1814538.0</t>
+          <t>1922596.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2484194.04</v>
+        <v>2486323.4</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>255558</t>
+          <t>179924</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-23797.97783740016</t>
+          <t>8205.679393326947</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>115375.5865989607</t>
+          <t>184225.794162326</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>3636910.0</t>
+          <t>3151324.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16831.658</t>
+          <t>11660.815</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.92</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.10</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.7</v>
+        <v>-0.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.38</v>
+        <v>-0.83</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>76.90000000000001</v>
+        <v>76.94</v>
       </c>
       <c r="BA11" t="n">
-        <v>76.51000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-63.14</t>
+          <t>-94.42</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-79.67</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1270686079.0</t>
+          <t>883348438.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>884981753.8</v>
+        <v>934882404.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1148148362.0</t>
+          <t>1080656940.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>890513194.8</v>
+        <v>901441468.14</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-263166608</t>
+          <t>-145774535</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>46396206.20353962</t>
+          <t>29056257.7153815</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-54065121.70841813</t>
+          <t>-66313458.96948814</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1270686079.0</t>
+          <t>883348438.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13356.417</t>
+          <t>16831.658</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>-22.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.25</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>33.10</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.17</v>
+        <v>-1.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.27</v>
+        <v>-0.38</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>76.59</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-26.14</t>
+          <t>-63.14</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-70.90</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1024663694.0</t>
+          <t>1270686079.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>755123165.2</v>
+        <v>884981753.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1307241707.2</t>
+          <t>1148148362.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>878310192.12</v>
+        <v>890513194.8</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-552118542</t>
+          <t>-263166608</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>64661902.18753193</t>
+          <t>46396206.20353962</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-76137061.38158941</t>
+          <t>-54065121.70841813</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1024663694.0</t>
+          <t>1270686079.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10628.462</t>
+          <t>13356.417</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,193 +6320,193 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-42.24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-10.25</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025/10/07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-53.90</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>-9.31</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025/10/07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>78.1</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2025-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>26.26</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>78.8</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>78.1</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2025-12-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6520,47 +6520,47 @@
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.14</v>
+        <v>0.27</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>76.66</v>
+        <v>76.59</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>77.36</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-26.14</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-69.00</t>
+          <t>-70.90</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>721871594.8</v>
+        <v>755123165.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1566009348.4</t>
+          <t>1307241707.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>874147139.14</v>
+        <v>878310192.12</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-844137753</t>
+          <t>-552118542</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>90261713.745554</t>
+          <t>64661902.18753193</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-78589681.75820565</t>
+          <t>-76137061.38158941</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>819770028.0</t>
+          <t>1024663694.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8791.772</t>
+          <t>10628.462</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-53.90</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,84 +6967,84 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.38</v>
+        <v>-1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.13</v>
+        <v>1.14</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>76.84</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="BA14" t="n">
-        <v>76.7</v>
+        <v>76.66</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="BE14" t="n">
         <v>0.48</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-68.96</t>
+          <t>-69.00</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>988114425.2</v>
+        <v>721871594.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1751817286.0</t>
+          <t>1566009348.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>866724470.7</v>
+        <v>874147139.14</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-763702860</t>
+          <t>-844137753</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>120961967.4735103</t>
+          <t>90261713.745554</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-57333758.01915002</t>
+          <t>-78589681.75820565</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>675943784.0</t>
+          <t>819770028.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8191.283</t>
+          <t>8791.772</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-2.01</v>
+        <v>-1.38</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>78.67999999999999</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>76.73999999999999</v>
+        <v>76.84</v>
       </c>
       <c r="BA15" t="n">
-        <v>76.73</v>
+        <v>76.7</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>77.38</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-70.45</t>
+          <t>-68.96</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1226431475.8</v>
+        <v>988114425.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1923628405.5</t>
+          <t>1751817286.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>861574179.78</v>
+        <v>866724470.7</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-697196929</t>
+          <t>-763702860</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>153379372.1085395</t>
+          <t>120961967.4735103</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-9510563.74838686</t>
+          <t>-57333758.01915002</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>633845184.0</t>
+          <t>675943784.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7923.656</t>
+          <t>8191.283</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.28</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>69.83</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.17</v>
+        <v>-2.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.67999999999999</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>76.66</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>76.77</v>
+        <v>76.73</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>77.38</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>85.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-73.49</t>
+          <t>-70.45</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1411314970.2</v>
+        <v>1226431475.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1967701017.6</t>
+          <t>1923628405.5</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>854744843.26</v>
+        <v>861574179.78</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-556386047</t>
+          <t>-697196929</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>182995724.0825261</t>
+          <t>153379372.1085395</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>63658512.48657465</t>
+          <t>-9510563.74838686</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>621393136.0</t>
+          <t>633845184.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10769.048</t>
+          <t>7923.656</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,84 +8268,84 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-28.28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>79.6</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-5.71</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-4.88</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,33 +8449,33 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>84.48</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>69.83</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.12</v>
+        <v>-1.17</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>76.59999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="BA17" t="n">
         <v>76.77</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>154.81</t>
+          <t>85.18</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-79.14</t>
+          <t>-73.49</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>1859360249.2</v>
+        <v>1411314970.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1954784789.8</t>
+          <t>1967701017.6</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>853657807.64</v>
+        <v>854744843.26</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-95424540</t>
+          <t>-556386047</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>204693398.9181536</t>
+          <t>182995724.0825261</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>167246393.9477129</t>
+          <t>63658512.48657465</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>858405842.0</t>
+          <t>621393136.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27059.373</t>
+          <t>10769.048</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.48</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>82.17</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>2.57</v>
+        <v>1.12</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>78.47999999999999</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>76.44</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>76.73</v>
+        <v>76.77</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>257.17</t>
+          <t>154.81</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-87.21</t>
+          <t>-79.14</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2410147102</v>
+        <v>1859360249.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1891076280.5</t>
+          <t>1954784789.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>844173360.7</v>
+        <v>853657807.64</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>519070821</t>
+          <t>-95424540</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>211501945.2764156</t>
+          <t>204693398.9181536</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>283861777.7512066</t>
+          <t>167246393.9477129</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>2150984180.0</t>
+          <t>858405842.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23927.778</t>
+          <t>27059.373</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>72.87</t>
+          <t>82.17</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.28</v>
+        <v>2.57</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>78.17999999999999</t>
+          <t>78.47999999999999</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>76.25</v>
+        <v>76.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>76.67</v>
+        <v>76.73</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>546.10</t>
+          <t>257.17</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-87.21</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1242773822.028689</t>
+          <t>1242942020.055215</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2515520146.8</v>
+        <v>2410147102</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1723525396.2</t>
+          <t>1891076280.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>811558988.24</v>
+        <v>844173360.7</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>791994750</t>
+          <t>519070821</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>198345612.0991808</t>
+          <t>211501945.2764156</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>301826726.3365116</t>
+          <t>283861777.7512066</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1867529037.0</t>
+          <t>2150984180.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>427856</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>462.207</t>
+          <t>1107.348</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>46.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.78</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>17.30</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,63 +9910,63 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.54</v>
+        <v>-1.38</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.64</v>
+        <v>14.63</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.85</v>
+        <v>14.84</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-29.90</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.11</v>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-276.24</t>
+          <t>-281.55</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>6601345.0</t>
+          <t>15977054.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>6180211.8</v>
+        <v>9005083.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>4773086.1</t>
+          <t>6160948.0</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>4209988</v>
+        <v>4467076.3</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>1407125</t>
+          <t>2844135</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>88172.71401964061</t>
+          <t>254417.778709953</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>467691.8524119155</t>
+          <t>1168765.634506671</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>6601345.0</t>
+          <t>15977054.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-13.07</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>554.629</t>
+          <t>462.207</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.40</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.50</t>
+          <t>-20.78</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>17.30</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10416,47 +10416,47 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.33</v>
+        <v>-1.54</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.68</v>
+        <v>14.64</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.87</v>
+        <v>14.85</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-27.67</t>
+          <t>-29.90</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-263.07</t>
+          <t>-276.24</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>7945767.0</t>
+          <t>6601345.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>5893366.8</v>
+        <v>6180211.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>4258184.0</t>
+          <t>4773086.1</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>4156786.06</v>
+        <v>4209988</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>1635182</t>
+          <t>1407125</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>19169.23431195425</t>
+          <t>88172.71401964061</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>453994.8475475535</t>
+          <t>467691.8524119155</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>7945767.0</t>
+          <t>6601345.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-12.77</t>
+          <t>-13.07</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10646,17 +10646,17 @@
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
           <t>14.3</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>14.35</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>791.96</t>
+          <t>554.629</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.40</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-20.22</t>
+          <t>-20.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,47 +10903,47 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.96</v>
+        <v>-0.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.11</v>
+        <v>-1.33</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.7</v>
+        <v>14.68</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-27.67</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-251.79</t>
+          <t>-263.07</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>5168210.4</v>
+        <v>5893366.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>3733648.1</t>
+          <t>4258184.0</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>4110798.74</v>
+        <v>4156786.06</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>1434562</t>
+          <t>1635182</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-59889.96809451834</t>
+          <t>19169.23431195425</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>274168.381757481</t>
+          <t>453994.8475475535</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>11410217.0</t>
+          <t>7945767.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.77</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>212.646</t>
+          <t>791.96</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,44 +11390,44 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.62</v>
+        <v>-0.96</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.97</v>
+        <v>-1.11</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
           <t>-1.16</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.9</v>
+        <v>14.89</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BE23" t="n">
         <v>-0.09</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-242.95</t>
+          <t>-251.79</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3236186.8</v>
+        <v>5168210.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2843595.6</t>
+          <t>3733648.1</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>3959256.34</v>
+        <v>4110798.74</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>392591</t>
+          <t>1434562</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-120627.849885791</t>
+          <t>-59889.96809451834</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-363709.3687196756</t>
+          <t>274168.381757481</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>3091035.0</t>
+          <t>11410217.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>127.048</t>
+          <t>212.646</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-19.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,48 +11877,48 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.91</v>
+        <v>-0.97</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.92</v>
+        <v>14.9</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="BD24" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BE24" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BE24" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="BF24" t="inlineStr">
         <is>
           <t>0.06</t>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-237.19</t>
+          <t>-242.95</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3316812.4</v>
+        <v>3236186.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2839807.1</t>
+          <t>2843595.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>3937193.46</v>
+        <v>3959256.34</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>477005</t>
+          <t>392591</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-76431.21009781194</t>
+          <t>-120627.849885791</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-370632.7490899111</t>
+          <t>-363709.3687196756</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1852695.0</t>
+          <t>3091035.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>354.44</t>
+          <t>127.048</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-19.11</t>
+          <t>-19.39</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,40 +12364,40 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.34</v>
+        <v>-0.48</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="BD25" t="n">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-233.09</t>
+          <t>-237.19</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>3365960.4</v>
+        <v>3316812.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>3016978.6</t>
+          <t>2839807.1</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>3926173.22</v>
+        <v>3937193.46</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>477005</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-22940.02119015754</t>
+          <t>-76431.21009781194</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-234607.122865608</t>
+          <t>-370632.7490899111</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>5167120.0</t>
+          <t>1852695.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,34 +12636,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>354.44</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>295.471</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-55.79</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,44 +12851,44 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.74</v>
+        <v>-0.86</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>14.79</v>
+        <v>14.78</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.94</v>
+        <v>14.93</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BE26" t="n">
         <v>-0.08</v>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-230.38</t>
+          <t>-233.09</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2623001.2</v>
+        <v>3365960.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>5932770.2</t>
+          <t>3016978.6</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>3872896.32</v>
+        <v>3926173.22</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-3309769</t>
+          <t>348981</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>15544.90638719709</t>
+          <t>-22940.02119015754</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-387022.9381571175</t>
+          <t>-234607.122865608</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>4319985.0</t>
+          <t>5167120.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13081,17 +13081,17 @@
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>14.6</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>14.65</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>119.496</t>
+          <t>295.471</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-60.05</t>
+          <t>-55.79</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,12 +13298,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,40 +13338,40 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.8</v>
+        <v>14.79</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="BD27" t="n">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-228.47</t>
+          <t>-230.38</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2299085.8</v>
+        <v>2623001.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>5755023.9</t>
+          <t>5932770.2</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>3887411.24</v>
+        <v>3872896.32</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-3455938</t>
+          <t>-3309769</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>88739.05994070883</t>
+          <t>15544.90638719709</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-500173.1050679483</t>
+          <t>-387022.9381571175</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1750099.0</t>
+          <t>4319985.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
@@ -13610,34 +13610,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>119.496</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>-0.34</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>238.503</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-59.23</t>
+          <t>-60.05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,44 +13821,44 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BD28" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-226.36</t>
+          <t>-228.47</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>10299422.54508197</t>
+          <t>10327369.6993865</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2451004.4</v>
+        <v>2299085.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>6011676.6</t>
+          <t>5755023.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3903777.52</v>
+        <v>3887411.24</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-3560672</t>
+          <t>-3455938</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>195813.999033192</t>
+          <t>88739.05994070883</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-368607.9469024232</t>
+          <t>-500173.1050679483</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>3494163.0</t>
+          <t>1750099.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
           <t>14.7</t>
-        </is>
-      </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>14.75</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">

--- a/Result/checksun_type/乳製品.xlsx
+++ b/Result/checksun_type/乳製品.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>269749.009090608</t>
+          <t>269749.0090906092</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>235755.7031582354</t>
+          <t>235755.7031582368</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>164685.8351268345</t>
+          <t>164685.8351268362</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>88746.21545881283</t>
+          <t>88746.21545881478</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>55697.9708154391</t>
+          <t>55697.97081544142</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9398.397184257108</t>
+          <t>-9398.397184254365</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>200519.1861652758</t>
+          <t>200519.1861652764</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-47565.23052053581</t>
+          <t>-47565.2305205327</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-173132.2971241865</t>
+          <t>-173132.2971241858</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-24734.85477441749</t>
+          <t>-24734.85477441394</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-79669.86978326901</t>
+          <t>-79669.86978326831</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-14746.67022735358</t>
+          <t>-14746.67022734951</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>18834.41462458717</t>
+          <t>18834.4146245881</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-20852.32201861554</t>
+          <t>-20852.32201861089</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>57977.37754207477</t>
+          <t>57977.37754207593</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>2058054.699203187</t>
+          <t>1494751.37007874</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-35184.99466601377</t>
+          <t>-35184.9946660085</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-151779.4746308739</t>
+          <t>-151779.4746308727</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6470,37 +6470,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-163.63</t>
+          <t>-162.86</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-62027120.65548377</t>
+          <t>-62027120.65547691</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-72956097.18075645</t>
+          <t>-72956097.18075502</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6967,37 +6967,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-160.54</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-60040034.01452511</t>
+          <t>-60040034.01451726</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-65209296.99971843</t>
+          <t>-65209296.99971676</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7464,37 +7464,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7519,12 +7519,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-156.67</t>
+          <t>-155.98</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-59100168.01721723</t>
+          <t>-59100168.01720826</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-51212719.38395989</t>
+          <t>-51212719.3839581</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7961,37 +7961,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-151.42</t>
+          <t>-150.80</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-60534249.58690039</t>
+          <t>-60534249.58689011</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-37145710.56202054</t>
+          <t>-37145710.56201839</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8458,37 +8458,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.72</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-146.13</t>
+          <t>-145.57</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-64786711.22778764</t>
+          <t>-64786711.22777587</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-54643597.33203506</t>
+          <t>-54643597.33203268</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8955,37 +8955,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="BA18" t="n">
         <v>75.81</v>
@@ -9169,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-141.22</t>
+          <t>-140.73</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-66630913.75428811</t>
+          <t>-66630913.75427464</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-51710307.20591176</t>
+          <t>-51710307.20590901</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -9452,37 +9452,37 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-136.35</t>
+          <t>-135.92</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-69343751.30853836</t>
+          <t>-69343751.30852292</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-73851198.41123879</t>
+          <t>-73851198.41123557</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -9949,37 +9949,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-131.59</t>
+          <t>-131.21</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-68524215.47168374</t>
+          <t>-68524215.47166608</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-77317754.83273304</t>
+          <t>-77317754.83272934</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10446,37 +10446,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-127.02</t>
+          <t>-126.69</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-66925390.13331114</t>
+          <t>-66925390.13329095</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-86026381.90512717</t>
+          <t>-86026381.90512288</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10943,37 +10943,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.72</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-122.15</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-63452482.5384355</t>
+          <t>-63452482.53841241</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-98139571.1547929</t>
+          <t>-98139571.15478802</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11440,37 +11440,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-118.08</t>
+          <t>-117.87</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1384354261.195219</t>
+          <t>1237900264.523622</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-57145739.15364324</t>
+          <t>-57145739.15361685</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-94402981.22021544</t>
+          <t>-94402981.22020984</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11937,37 +11937,37 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -11992,22 +11992,22 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -12151,12 +12151,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-398.18</t>
+          <t>-189.68</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12192,12 +12192,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-210987.309384789</t>
+          <t>-210987.3093845762</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-521476.6048400388</t>
+          <t>-521476.6048399941</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -12434,37 +12434,37 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -12489,22 +12489,22 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20.50</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-404.13</t>
+          <t>-191.47</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-154534.7102111072</t>
+          <t>-154534.7102108639</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-374193.0959258056</t>
+          <t>-374193.0959257544</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -12931,37 +12931,37 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -12986,22 +12986,22 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-414.20</t>
+          <t>-194.50</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-114596.8218993438</t>
+          <t>-114596.8218990656</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-272815.3654795503</t>
+          <t>-272815.3654794917</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -13428,37 +13428,37 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -13483,22 +13483,22 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13642,12 +13642,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-438.16</t>
+          <t>-201.70</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-85829.81397566988</t>
+          <t>-85829.8139753518</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-267496.5232177731</t>
+          <t>-267496.523217706</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -13925,37 +13925,37 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -13980,22 +13980,22 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -14139,12 +14139,12 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-476.38</t>
+          <t>-213.20</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-52799.5032043784</t>
+          <t>-52799.50320401469</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-156471.5155860288</t>
+          <t>-156471.5155859515</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -14422,37 +14422,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -14477,22 +14477,22 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.11</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-507.22</t>
+          <t>-222.47</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-33950.04640771469</t>
+          <t>-33950.0464072989</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-128638.3076983215</t>
+          <t>-128638.3076982331</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -14919,37 +14919,37 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -14959,12 +14959,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -14974,22 +14974,22 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -15014,12 +15014,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-546.19</t>
+          <t>-234.19</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-16733.99890033162</t>
+          <t>-16733.99889985632</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-134415.4640123704</t>
+          <t>-134415.4640122699</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -15416,37 +15416,37 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -15471,22 +15471,22 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15630,12 +15630,12 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-575.26</t>
+          <t>-242.94</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>4662.631120039077</t>
+          <t>4662.631120582511</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-223198.3850319991</t>
+          <t>-223198.3850318836</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -15846,12 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -15913,37 +15913,37 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -15953,12 +15953,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -15968,22 +15968,22 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>-601.78</t>
+          <t>-250.91</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16168,12 +16168,12 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>46091.90678404602</t>
+          <t>46091.90678466726</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>-185180.8655946115</t>
+          <t>-185180.8655944793</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -16343,12 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -16410,37 +16410,37 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -16450,12 +16450,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -16465,22 +16465,22 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20.50</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>-623.75</t>
+          <t>-257.52</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>88141.50176198376</t>
+          <t>88141.50176269391</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>-92925.59262710717</t>
+          <t>-92925.59262695536</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16840,12 +16840,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -16907,37 +16907,37 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-05 00:00:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-16 00:00:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-21 00:00:00</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -16947,12 +16947,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -16962,22 +16962,22 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -17121,12 +17121,12 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>-638.44</t>
+          <t>-261.94</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>7884667.966135458</t>
+          <t>10188418.7273622</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -17162,12 +17162,12 @@
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>121062.7916509094</t>
+          <t>121062.791651721</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>-124058.2529368475</t>
+          <t>-124058.2529366743</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
